--- a/Дело3а-78-2026Таганай/09_Нормативка/00_Ведомость_09_Нормативные_акты.xlsx
+++ b/Дело3а-78-2026Таганай/09_Нормативка/00_Ведомость_09_Нормативные_акты.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ведомость 09" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ведомость 09'!$B$11:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ведомость 09'!$B$11:$H$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Ведомость 09'!$1:$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+    <numFmt numFmtId="165" formatCode="dd.mm.yyyy"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -128,8 +128,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F4EC"/>
-        <bgColor rgb="00E8F4EC"/>
+        <fgColor rgb="00FFF6CC"/>
+        <bgColor rgb="00FFF6CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H29"/>
+  <dimension ref="B2:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -622,11 +622,11 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>2.93 МБ</t>
+          <t>2.91 МБ</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>46157.92969592741</v>
+        <v>46158.29722373497</v>
       </c>
     </row>
     <row r="9">
@@ -687,12 +687,12 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>442-FZ кандидат</t>
+          <t>442-FZ от 28.12.2013</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>09.1_442-FZ_кандидат.pdf</t>
+          <t>09.1_442-FZ_от_28.12.2013.pdf</t>
         </is>
       </c>
       <c r="E12" s="13" t="n">
@@ -718,12 +718,12 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>557-P кандидат</t>
+          <t>Постановление 557-П от 25.06.2021</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>09.2_557-P_кандидат.pdf</t>
+          <t>09.2_Постановление_557-П_от_25.06.2021.pdf</t>
         </is>
       </c>
       <c r="E13" s="13" t="n">
@@ -785,15 +785,15 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>09.5_Постановление_РФ_№1236_от_24.11.2014.docx</t>
+          <t>09.5_Постановление_РФ_№1236_от_24.11.2014.pdf</t>
         </is>
       </c>
       <c r="E15" s="13" t="n">
-        <v>46157.58168981481</v>
+        <v>46157.58170138889</v>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>12 КБ</t>
+          <t>141 КБ</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr"/>
@@ -806,25 +806,25 @@
     <row r="16" ht="32" customHeight="1">
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>09.5</t>
+          <t>09.6</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Постановление РФ №1236 от 24.11.2014</t>
+          <t>Постановление Правительства РФ от 01.12.2014 № 1285</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>09.5_Постановление_РФ_№1236_от_24.11.2014.pdf</t>
+          <t>09.6_Постановление Правительства РФ от 01.12.2014 № 1285.pdf</t>
         </is>
       </c>
       <c r="E16" s="13" t="n">
-        <v>46157.58170138889</v>
+        <v>46140.72214230907</v>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>141 КБ</t>
+          <t>604 КБ</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr"/>
@@ -837,25 +837,25 @@
     <row r="17" ht="32" customHeight="1">
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>09.6</t>
+          <t>09.7</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Постановление Правительства РФ от 01.12.2014 № 1285</t>
+          <t>Постановление Правительства ЯНАО от 25.12.2015 № 1306-П</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>09.6_Постановление Правительства РФ от 01.12.2014 № 1285.pdf</t>
+          <t>09.7_Постановление Правительства ЯНАО от 25.12.2015 № 1306-П.pdf</t>
         </is>
       </c>
       <c r="E17" s="13" t="n">
-        <v>46140.72214230907</v>
+        <v>46140.72978671999</v>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>604 КБ</t>
+          <t>275 КБ</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr"/>
@@ -868,25 +868,25 @@
     <row r="18" ht="32" customHeight="1">
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>09.7</t>
+          <t>09.8</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Постановление Правительства ЯНАО от 25.12.2015 № 1306-П</t>
+          <t>Постановление Правительства ЯНАО от 13.03.2026 № 129-П</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>09.7_Постановление Правительства ЯНАО от 25.12.2015 № 1306-П.pdf</t>
+          <t>09.8_Постановление Правительства ЯНАО от 13.03.2026 № 129-П.pdf</t>
         </is>
       </c>
       <c r="E18" s="13" t="n">
-        <v>46140.72978671999</v>
+        <v>46140.77170517622</v>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>275 КБ</t>
+          <t>191 КБ</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr"/>
@@ -899,25 +899,25 @@
     <row r="19" ht="32" customHeight="1">
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>09.8</t>
+          <t>09.9</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Постановление Правительства ЯНАО от 13.03.2026 № 129-П</t>
+          <t>Диаграмма динамики инфляции ЯНАО и России 2019–2025 гг.</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>09.8_Постановление Правительства ЯНАО от 13.03.2026 № 129-П.pdf</t>
+          <t>09.9_Диаграмма динамики инфляции ЯНАО и России 2019–2025 гг..pdf</t>
         </is>
       </c>
       <c r="E19" s="13" t="n">
-        <v>46140.77170517622</v>
+        <v>46140.68394272676</v>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>191 КБ</t>
+          <t>402 КБ</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr"/>
@@ -927,116 +927,54 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>09.9</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Диаграмма динамики инфляции ЯНАО и России 2019–2025 гг.</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>09.9_Диаграмма динамики инфляции ЯНАО и России 2019–2025 гг..pdf</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="n">
-        <v>46140.68394272676</v>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>402 КБ</t>
-        </is>
-      </c>
-      <c r="G20" s="15" t="inlineStr"/>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>_____________</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>09.10</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Сводная ведомость</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Сводная_ведомость.xlsx</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="n">
-        <v>46157.92521207507</v>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>8 КБ</t>
-        </is>
-      </c>
-      <c r="G21" s="15" t="inlineStr"/>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>_____________</t>
+    <row r="22">
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Председатель правления РКООИ ЦИП «Таганай»: Богдановский С.В.    ____________________</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>Председатель правления РКООИ ЦИП «Таганай»: Богдановский С.В.    ____________________</t>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>Подсказки:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>• Колонка «Наименование документа» заполнена автоматически по имени файла — проверьте формулировки.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>Подсказки:</t>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>• Колонка «Стр.» (G) — для PDF укажите число страниц при необходимости.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>• Колонка «Наименование документа» заполнена автоматически по имени файла — проверьте формулировки.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>• Колонка «Стр.» (G) — для PDF укажите число страниц при необходимости.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="19" t="inlineStr">
-        <is>
           <t>• Перезапуск скрипта перезапишет файл (в т.ч. наименования).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B11:H21"/>
+  <autoFilter ref="B11:H19"/>
   <mergeCells count="10">
+    <mergeCell ref="B22:H22"/>
     <mergeCell ref="E9:H9"/>
+    <mergeCell ref="B26:H26"/>
     <mergeCell ref="B27:H27"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B24:H24"/>
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B25:H25"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B28:H28"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/Дело3а-78-2026Таганай/09_Нормативка/00_Ведомость_09_Нормативные_акты.xlsx
+++ b/Дело3а-78-2026Таганай/09_Нормативка/00_Ведомость_09_Нормативные_акты.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>46158.29722373497</v>
+        <v>46158.37379341062</v>
       </c>
     </row>
     <row r="9">
